--- a/data/trans_camb/P6906-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 23,01</t>
+          <t>-12,6; 22,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 33,69</t>
+          <t>-3,13; 33,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 13,92</t>
+          <t>-21,31; 16,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 25,09</t>
+          <t>-15,19; 23,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 33,56</t>
+          <t>-5,0; 33,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 27,33</t>
+          <t>-6,02; 27,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 19,94</t>
+          <t>-7,28; 17,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 28,1</t>
+          <t>0,78; 28,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 16,11</t>
+          <t>-8,47; 15,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 98,61</t>
+          <t>-31,95; 102,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 137,3</t>
+          <t>-8,24; 143,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 63,7</t>
+          <t>-57,49; 71,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-33,13; 165,73</t>
+          <t>-43,97; 136,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 206,05</t>
+          <t>-16,71; 199,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 171,42</t>
+          <t>-18,29; 182,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 89,83</t>
+          <t>-21,2; 78,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 118,55</t>
+          <t>1,44; 122,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 74,0</t>
+          <t>-26,0; 70,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 25,41</t>
+          <t>-10,44; 27,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 34,87</t>
+          <t>-12,24; 33,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 18,76</t>
+          <t>-19,58; 17,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,2; 22,19</t>
+          <t>-20,72; 22,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 24,44</t>
+          <t>-15,87; 24,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 26,11</t>
+          <t>-8,61; 28,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 17,92</t>
+          <t>-11,94; 17,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 23,21</t>
+          <t>-7,37; 23,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 16,45</t>
+          <t>-10,24; 15,55</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,41; 214,41</t>
+          <t>-39,69; 259,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-45,52; 334,74</t>
+          <t>-48,42; 284,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-64,34; 184,61</t>
+          <t>-67,41; 161,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,57; 147,86</t>
+          <t>-66,71; 178,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,42; 183,24</t>
+          <t>-53,85; 163,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 202,22</t>
+          <t>-28,28; 237,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 121,17</t>
+          <t>-44,74; 118,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 173,91</t>
+          <t>-26,62; 151,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 119,14</t>
+          <t>-35,5; 112,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 6,87</t>
+          <t>-20,36; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 5,82</t>
+          <t>-23,13; 5,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 6,64</t>
+          <t>-25,23; 5,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 37,27</t>
+          <t>-13,92; 35,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 64,66</t>
+          <t>-10,61; 62,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 39,76</t>
+          <t>-15,71; 38,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 7,9</t>
+          <t>-15,66; 8,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,75; 8,38</t>
+          <t>-18,05; 9,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 6,63</t>
+          <t>-18,68; 7,79</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,41; 29,29</t>
+          <t>-59,05; 29,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,53; 30,84</t>
+          <t>-67,73; 27,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,25; 30,29</t>
+          <t>-74,2; 34,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,72; 38,97</t>
+          <t>-48,47; 44,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,5; 42,34</t>
+          <t>-56,24; 43,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,37; 35,63</t>
+          <t>-59,82; 37,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 12,05</t>
+          <t>-6,94; 13,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 12,04</t>
+          <t>-6,3; 12,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 11,4</t>
+          <t>-7,59; 12,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 17,64</t>
+          <t>-13,0; 21,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 23,34</t>
+          <t>-8,36; 24,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 12,9</t>
+          <t>-14,4; 12,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 12,77</t>
+          <t>-5,21; 11,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 14,03</t>
+          <t>-1,72; 14,76</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 9,42</t>
+          <t>-6,21; 10,35</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,28; 73,6</t>
+          <t>-30,02; 81,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 76,5</t>
+          <t>-27,03; 75,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 70,64</t>
+          <t>-35,23; 71,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,0; 100,93</t>
+          <t>-38,37; 140,05</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 133,56</t>
+          <t>-23,45; 149,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 75,76</t>
+          <t>-40,47; 81,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 72,43</t>
+          <t>-21,06; 65,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 81,76</t>
+          <t>-7,46; 83,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 54,15</t>
+          <t>-24,26; 63,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 31,34</t>
+          <t>-1,46; 32,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 8,97</t>
+          <t>-13,59; 9,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 5,26</t>
+          <t>-17,56; 4,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 35,52</t>
+          <t>-0,67; 34,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 26,05</t>
+          <t>-7,55; 24,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 10,84</t>
+          <t>-14,74; 11,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 27,47</t>
+          <t>4,53; 27,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 9,97</t>
+          <t>-7,21; 11,5</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 7,79</t>
+          <t>-10,59; 7,22</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,39; 519,26</t>
+          <t>-23,57; 443,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,87; 162,42</t>
+          <t>-77,82; 187,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 152,36</t>
+          <t>-100,0; 127,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 350,8</t>
+          <t>-12,72; 319,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 230,0</t>
+          <t>-33,42; 245,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 88,53</t>
+          <t>-60,59; 91,43</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,96; 276,6</t>
+          <t>18,3; 277,86</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 94,45</t>
+          <t>-39,52; 115,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-50,82; 71,44</t>
+          <t>-56,37; 66,42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1704,47 +1704,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,38</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3,61</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,91</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,0</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,1</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,95</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,16</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,41; 9,42</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,53; 6,93</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-9,5; 3,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,48; 16,53</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,42; 18,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,59; 10,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,21; 10,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,13; 10,11</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,57; 4,62</t>
         </is>
       </c>
     </row>
@@ -1810,47 +1810,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-15,97%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-0,7%</t>
         </is>
       </c>
     </row>
@@ -1863,282 +1863,65 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-13,63; 47,86</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,49; 34,02</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-38,55; 17,02</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,19; 95,64</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,55; 103,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-21,76; 57,94</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,85; 52,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,47; 51,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,82; 23,88</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>3,38</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-3,61</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>7,91</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>11,0</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>3,53</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4,95</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n"/>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>-3,14; 9,55</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>-5,03; 7,37</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>-9,4; 3,0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>-0,73; 16,64</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>2,68; 19,31</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>-5,68; 11,13</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 10,55</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 10,4</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>-5,43; 4,37</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>14,97%</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>5,79%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-15,97%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>36,54%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>50,8%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>16,29%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>22,9%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>-0,7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n"/>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>-12,59; 45,57</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>-20,12; 36,23</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-37,97; 14,6</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-2,97; 94,27</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>10,84; 111,27</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>-19,66; 62,03</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>0,85; 51,52</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 50,55</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>-22,16; 22,36</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="A24:A27"/>

--- a/data/trans_camb/P6906-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P6906-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-4,8</t>
+          <t>-3,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,59</t>
+          <t>9,92</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>3,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,6; 22,97</t>
+          <t>-10,72; 25,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 33,6</t>
+          <t>-6,0; 36,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 16,18</t>
+          <t>-20,64; 16,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 23,62</t>
+          <t>-11,03; 26,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 33,56</t>
+          <t>-5,52; 32,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 27,55</t>
+          <t>-7,63; 26,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 17,67</t>
+          <t>-8,18; 18,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 28,8</t>
+          <t>-0,43; 27,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 15,52</t>
+          <t>-8,68; 16,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-15,09%</t>
+          <t>-9,58%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,95; 102,19</t>
+          <t>-28,59; 109,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 143,04</t>
+          <t>-14,48; 152,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-57,49; 71,37</t>
+          <t>-52,22; 74,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,97; 136,67</t>
+          <t>-34,12; 159,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 199,44</t>
+          <t>-20,01; 196,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,29; 182,46</t>
+          <t>-22,97; 156,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 78,74</t>
+          <t>-23,7; 81,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 122,99</t>
+          <t>-2,15; 113,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,0; 70,2</t>
+          <t>-24,7; 68,66</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,87</t>
+          <t>3,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 27,48</t>
+          <t>-12,87; 27,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 33,26</t>
+          <t>-10,58; 32,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 17,81</t>
+          <t>-18,01; 19,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 22,56</t>
+          <t>-21,2; 21,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,87; 24,0</t>
+          <t>-16,42; 24,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 28,93</t>
+          <t>-9,84; 25,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 17,28</t>
+          <t>-10,16; 18,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 23,44</t>
+          <t>-5,91; 22,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 15,55</t>
+          <t>-10,19; 16,49</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,59%</t>
+          <t>-3,43%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 259,19</t>
+          <t>-45,9; 257,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 284,22</t>
+          <t>-45,19; 280,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 161,38</t>
+          <t>-66,65; 183,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-66,71; 178,45</t>
+          <t>-73,34; 158,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 163,11</t>
+          <t>-57,54; 178,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 237,87</t>
+          <t>-33,18; 212,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 118,68</t>
+          <t>-38,36; 115,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 151,42</t>
+          <t>-24,55; 157,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 112,27</t>
+          <t>-35,47; 112,37</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-11,29</t>
+          <t>-8,19</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,61</t>
+          <t>19,19</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,01</t>
+          <t>-3,35</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 6,66</t>
+          <t>-20,61; 6,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 5,28</t>
+          <t>-23,77; 4,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 5,81</t>
+          <t>-21,83; 9,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 35,9</t>
+          <t>-18,33; 37,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 62,64</t>
+          <t>-8,85; 70,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 38,24</t>
+          <t>-16,97; 39,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 8,66</t>
+          <t>-15,08; 8,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 9,35</t>
+          <t>-17,04; 11,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 7,79</t>
+          <t>-16,57; 11,02</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-39,02%</t>
+          <t>-28,3%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>173,73%</t>
+          <t>179,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-22,79%</t>
+          <t>-12,71%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,05; 29,8</t>
+          <t>-57,73; 30,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,73; 27,57</t>
+          <t>-67,67; 18,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,2; 34,71</t>
+          <t>-65,89; 50,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 44,23</t>
+          <t>-46,98; 45,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,24; 43,92</t>
+          <t>-54,52; 53,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,82; 37,21</t>
+          <t>-54,85; 55,88</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>3,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 13,01</t>
+          <t>-7,23; 13,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 12,68</t>
+          <t>-6,74; 12,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 12,25</t>
+          <t>-5,59; 13,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 21,86</t>
+          <t>-14,11; 20,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 24,02</t>
+          <t>-8,33; 23,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 12,8</t>
+          <t>-15,25; 13,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 11,87</t>
+          <t>-4,28; 12,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 14,76</t>
+          <t>-1,62; 14,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 10,35</t>
+          <t>-4,25; 10,73</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-2,85%</t>
+          <t>-1,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,02; 81,18</t>
+          <t>-30,38; 79,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,03; 75,37</t>
+          <t>-28,12; 77,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 71,54</t>
+          <t>-26,57; 82,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 140,05</t>
+          <t>-38,69; 120,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 149,05</t>
+          <t>-24,43; 152,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 81,41</t>
+          <t>-41,19; 80,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 65,1</t>
+          <t>-17,78; 70,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 83,08</t>
+          <t>-6,34; 83,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 63,17</t>
+          <t>-18,07; 58,95</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-6,31</t>
+          <t>-7,59</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>5,91</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,95</t>
+          <t>1,12</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 32,16</t>
+          <t>-0,61; 33,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 9,14</t>
+          <t>-13,89; 9,2</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-17,56; 4,53</t>
+          <t>-19,1; 2,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 34,69</t>
+          <t>-1,28; 35,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 24,36</t>
+          <t>-7,15; 23,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 11,42</t>
+          <t>-5,54; 17,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,53; 27,82</t>
+          <t>3,3; 27,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 11,5</t>
+          <t>-8,67; 11,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 7,22</t>
+          <t>-6,79; 8,89</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-51,62%</t>
+          <t>-62,09%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,44%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-6,44%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,57; 443,74</t>
+          <t>-17,26; 573,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,82; 187,96</t>
+          <t>-79,39; 163,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 127,41</t>
+          <t>-100,0; 95,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 319,37</t>
+          <t>-14,13; 344,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 245,35</t>
+          <t>-35,55; 212,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-60,59; 91,43</t>
+          <t>-22,9; 160,59</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,3; 277,86</t>
+          <t>16,23; 270,47</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 115,98</t>
+          <t>-44,89; 114,24</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 66,42</t>
+          <t>-34,08; 93,43</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-2,48</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,53</t>
+          <t>6,17</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>1,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 9,42</t>
+          <t>-2,47; 9,86</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 6,93</t>
+          <t>-5,1; 7,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 3,13</t>
+          <t>-8,54; 3,63</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 16,53</t>
+          <t>-0,37; 15,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,42; 18,71</t>
+          <t>3,18; 19,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 10,31</t>
+          <t>-0,65; 12,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 10,42</t>
+          <t>0,02; 9,98</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 10,11</t>
+          <t>0,24; 10,14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,62</t>
+          <t>-2,79; 6,1</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-15,97%</t>
+          <t>-10,96%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,7%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 47,86</t>
+          <t>-10,88; 48,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 34,02</t>
+          <t>-19,97; 37,24</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 17,02</t>
+          <t>-34,33; 18,51</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 95,64</t>
+          <t>-2,94; 89,47</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,55; 103,49</t>
+          <t>11,75; 106,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 57,94</t>
+          <t>-2,41; 71,12</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,85; 52,3</t>
+          <t>0,11; 50,41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 51,44</t>
+          <t>1,01; 49,18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-22,82; 23,88</t>
+          <t>-11,64; 30,38</t>
         </is>
       </c>
     </row>
